--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,766 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9691,0.0034,0.0084,0.0006</t>
-  </si>
-  <si>
-    <t>0.0307,0.0005,0.0002,0.9920</t>
-  </si>
-  <si>
-    <t>0.9828,0.0032,0.0008,0.0039</t>
-  </si>
-  <si>
-    <t>0.7713,0.0019,0.0007,0.1634</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9819,0.0019,0.0039,0.0002</t>
+  </si>
+  <si>
+    <t>0.0902,0.0024,0.0008,0.9632</t>
+  </si>
+  <si>
+    <t>0.9907,0.0010,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.9197,0.0012,0.0001,0.0392</t>
+  </si>
+  <si>
+    <t>0.9972,0.0015,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9867,0.0130,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9987,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9794,0.0166,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9496,0.0583,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.9944,0.0045,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0013,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.8273,0.0516,0.0388,0.0011</t>
+  </si>
+  <si>
+    <t>0.0298,0.0054,0.9491,0.0010</t>
+  </si>
+  <si>
+    <t>0.3503,0.0037,0.7814,0.0001</t>
+  </si>
+  <si>
+    <t>0.0655,0.0051,0.9330,0.0002</t>
+  </si>
+  <si>
+    <t>0.6972,0.0016,0.3210,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0034,0.0000</t>
+  </si>
+  <si>
+    <t>0.0412,0.9519,0.0150,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.9989,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.6968,0.0012,0.3481,0.0006</t>
+  </si>
+  <si>
+    <t>0.2958,0.0021,0.7673,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0022,0.9961,0.0014</t>
+  </si>
+  <si>
+    <t>0.0039,0.0006,0.9932,0.0006</t>
+  </si>
+  <si>
+    <t>0.0029,0.0002,0.9965,0.0001</t>
+  </si>
+  <si>
+    <t>0.5777,0.0005,0.5404,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9988,0.0011</t>
+  </si>
+  <si>
+    <t>0.0042,0.9953,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.1154,0.5337,0.1984,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9998,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0021,0.0000</t>
+  </si>
+  <si>
+    <t>0.9934,0.0053,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.8033,0.0246,0.0630,0.0005</t>
+  </si>
+  <si>
+    <t>0.0446,0.9336,0.0326,0.0011</t>
+  </si>
+  <si>
+    <t>0.0007,0.9961,0.0159,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.9609,0.1956,0.0086</t>
+  </si>
+  <si>
+    <t>0.0108,0.0152,0.9725,0.0016</t>
+  </si>
+  <si>
+    <t>0.0017,0.0161,0.9944,0.0001</t>
+  </si>
+  <si>
+    <t>0.0205,0.0002,0.9842,0.0002</t>
+  </si>
+  <si>
+    <t>0.0089,0.0139,0.9762,0.0012</t>
+  </si>
+  <si>
+    <t>0.0001,0.9991,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9993,0.0004</t>
+  </si>
+  <si>
+    <t>0.0024,0.9429,0.0088,0.5565</t>
+  </si>
+  <si>
+    <t>0.0015,0.9951,0.0040,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9998,0.0007</t>
+  </si>
+  <si>
+    <t>0.0010,0.6583,0.9496,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.0006,0.9937,0.0014</t>
+  </si>
+  <si>
+    <t>0.0047,0.0002,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0027,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.9745,0.0296,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9758,0.0136,0.0046,0.0016</t>
+  </si>
+  <si>
+    <t>0.9475,0.0625,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0028,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9935,0.0064,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.5331,0.5440,0.0081,0.0002</t>
+  </si>
+  <si>
+    <t>0.9800,0.0302,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9941,0.7591,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0245,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0067,0.0426,0.9735,0.0016</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9992,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.6993,0.0087,0.3206,0.0004</t>
+  </si>
+  <si>
+    <t>0.1560,0.0117,0.8588,0.0009</t>
+  </si>
+  <si>
+    <t>0.0052,0.5287,0.9382,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9891,0.9968,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9900,0.1293,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.0111,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.9938,0.6488,0.0000</t>
+  </si>
+  <si>
+    <t>0.0046,0.0000,0.0114,0.9925</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0094,0.0009,0.0000,0.9982</t>
+  </si>
+  <si>
+    <t>0.0008,0.0003,0.0009,0.9990</t>
+  </si>
+  <si>
+    <t>0.0041,0.0001,0.0028,0.9966</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0109,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.9718,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9623,0.9847,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9826,0.4928,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.7682,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9956,0.5794,0.0000</t>
   </si>
   <si>
     <t>0.9994,0.0003,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9970,0.0017,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9981,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9078,0.1096,0.0036,0.0008</t>
-  </si>
-  <si>
-    <t>0.9588,0.0524,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9931,0.0052,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9977,0.0009,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9100,0.0319,0.0124,0.0004</t>
-  </si>
-  <si>
-    <t>0.0682,0.0195,0.8934,0.0001</t>
-  </si>
-  <si>
-    <t>0.0876,0.0136,0.9311,0.0001</t>
-  </si>
-  <si>
-    <t>0.0305,0.0051,0.9678,0.0001</t>
-  </si>
-  <si>
-    <t>0.9274,0.0031,0.0395,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9992,0.0072,0.0000</t>
-  </si>
-  <si>
-    <t>0.0248,0.9538,0.0499,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.4077,0.0012,0.6534,0.0010</t>
-  </si>
-  <si>
-    <t>0.6598,0.0083,0.2863,0.0016</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.0662,0.0035,0.9316,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0223,0.0011,0.9736,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.0090,0.9869,0.0049,0.0013</t>
-  </si>
-  <si>
-    <t>0.2128,0.7195,0.0234,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0013</t>
-  </si>
-  <si>
-    <t>0.0002,0.9986,0.0052,0.0000</t>
-  </si>
-  <si>
-    <t>0.9428,0.0556,0.0006,0.0013</t>
-  </si>
-  <si>
-    <t>0.1377,0.0203,0.7636,0.0010</t>
-  </si>
-  <si>
-    <t>0.0327,0.9422,0.0321,0.0006</t>
-  </si>
-  <si>
-    <t>0.0007,0.9962,0.0104,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.2311,0.9230,0.0026</t>
-  </si>
-  <si>
-    <t>0.0184,0.0026,0.9747,0.0009</t>
-  </si>
-  <si>
-    <t>0.0291,0.0339,0.9367,0.0018</t>
-  </si>
-  <si>
-    <t>0.0090,0.0002,0.9920,0.0002</t>
-  </si>
-  <si>
-    <t>0.0008,0.0594,0.9970,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9968,0.0150,0.0005</t>
-  </si>
-  <si>
-    <t>0.0010,0.0006,0.9965,0.0020</t>
-  </si>
-  <si>
-    <t>0.0000,0.9921,0.0006,0.8149</t>
-  </si>
-  <si>
-    <t>0.0006,0.9977,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.9976,0.0028,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.7666,0.9706,0.0000</t>
-  </si>
-  <si>
-    <t>0.0050,0.0007,0.9913,0.0007</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9997,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0283,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.9886,0.0096,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9945,0.0041,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.8575,0.1272,0.0129,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0105,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9684,0.0369,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9560,0.0614,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.8956,0.1707,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9880,0.8440,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0040,0.9983,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.0028,0.9975,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9981,0.9974,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9991,0.0001,0.0000</t>
+    <t>0.6560,0.4294,0.0031,0.0001</t>
+  </si>
+  <si>
+    <t>0.4744,0.6217,0.0034,0.0002</t>
+  </si>
+  <si>
+    <t>0.9472,0.0481,0.0014,0.0011</t>
+  </si>
+  <si>
+    <t>0.9948,0.0043,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9907,0.0083,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9948,0.0053,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.7198,0.3294,0.0066,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0008,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0020,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9924,0.0087,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9248,0.1282,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9949,0.0038,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0055,0.0005,0.9950,0.0002</t>
+  </si>
+  <si>
+    <t>0.0146,0.0031,0.9907,0.0000</t>
+  </si>
+  <si>
+    <t>0.7645,0.0016,0.2100,0.0021</t>
+  </si>
+  <si>
+    <t>0.0061,0.0003,0.9957,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9991,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0054,0.9913,0.0055,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.9957,0.0086,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0049,0.0000</t>
+  </si>
+  <si>
+    <t>0.0537,0.9466,0.0074,0.0001</t>
+  </si>
+  <si>
+    <t>0.3347,0.0102,0.6436,0.0006</t>
+  </si>
+  <si>
+    <t>0.7214,0.0226,0.1738,0.0004</t>
+  </si>
+  <si>
+    <t>0.1276,0.2266,0.2131,0.0098</t>
+  </si>
+  <si>
+    <t>0.0580,0.0057,0.9166,0.0013</t>
+  </si>
+  <si>
+    <t>0.0014,0.3310,0.0061,0.9050</t>
+  </si>
+  <si>
+    <t>0.0003,0.9982,0.0080,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.9977,0.0043,0.0000</t>
   </si>
   <si>
     <t>0.0001,0.9997,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.8180,0.0091,0.1799,0.0006</t>
-  </si>
-  <si>
-    <t>0.2853,0.0194,0.7221,0.0005</t>
-  </si>
-  <si>
-    <t>0.0013,0.1993,0.9897,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9952,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9858,0.7788,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.0319,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9969,0.9527,0.0000</t>
-  </si>
-  <si>
-    <t>0.0158,0.0001,0.0264,0.9694</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0021,0.0001,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0017,0.0003,0.0016,0.9982</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.0038,0.9986</t>
-  </si>
-  <si>
-    <t>0.0021,0.0002,0.0001,0.9992</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0082,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.9848,0.9326,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.8348,0.9592,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9847,0.6551,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9966,0.6766,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.2848,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0017,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9121,0.1023,0.0025,0.0004</t>
-  </si>
-  <si>
-    <t>0.3306,0.7557,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.9871,0.0136,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9924,0.0055,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9458,0.0590,0.0031,0.0008</t>
-  </si>
-  <si>
-    <t>0.4744,0.6073,0.0041,0.0003</t>
-  </si>
-  <si>
-    <t>0.7367,0.2889,0.0106,0.0004</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9948,0.0054,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9967,0.0028,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0019,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.8877,0.1645,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9933,0.0063,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0007,0.9980,0.0004</t>
-  </si>
-  <si>
-    <t>0.0542,0.0074,0.9589,0.0001</t>
-  </si>
-  <si>
-    <t>0.9894,0.0001,0.0048,0.0000</t>
-  </si>
-  <si>
-    <t>0.0041,0.0003,0.9963,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0059,0.9904,0.0059,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9981,0.0072,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0045,0.0000</t>
-  </si>
-  <si>
-    <t>0.0256,0.9679,0.0106,0.0001</t>
-  </si>
-  <si>
-    <t>0.3408,0.0067,0.6216,0.0011</t>
-  </si>
-  <si>
-    <t>0.0944,0.0236,0.8366,0.0006</t>
-  </si>
-  <si>
-    <t>0.3522,0.0265,0.4562,0.0025</t>
-  </si>
-  <si>
-    <t>0.0416,0.0089,0.9138,0.0035</t>
-  </si>
-  <si>
-    <t>0.0053,0.8130,0.0206,0.4713</t>
-  </si>
-  <si>
-    <t>0.0002,0.9992,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9991,0.0031,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9991,0.0124,0.0000</t>
-  </si>
-  <si>
-    <t>0.1619,0.8334,0.0192,0.0007</t>
-  </si>
-  <si>
-    <t>0.0916,0.8625,0.0808,0.0009</t>
-  </si>
-  <si>
-    <t>0.9987,0.0009,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9962,0.0008,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0006,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0004,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0011,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9953,0.0054,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9828,0.0098,0.0021,0.0018</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.3409,0.9939,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.6201,0.9913,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.1427,0.9784,0.0001</t>
-  </si>
-  <si>
-    <t>0.0235,0.0384,0.9653,0.0001</t>
-  </si>
-  <si>
-    <t>0.9875,0.0006,0.0038,0.0000</t>
-  </si>
-  <si>
-    <t>0.2926,0.0066,0.6883,0.0012</t>
-  </si>
-  <si>
-    <t>0.0068,0.0009,0.9947,0.0002</t>
-  </si>
-  <si>
-    <t>0.8762,0.0065,0.0880,0.0005</t>
-  </si>
-  <si>
-    <t>0.2491,0.0002,0.0003,0.9203</t>
+    <t>0.0869,0.8872,0.0426,0.0010</t>
+  </si>
+  <si>
+    <t>0.0725,0.9085,0.0326,0.0010</t>
+  </si>
+  <si>
+    <t>0.9895,0.0106,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9962,0.0015,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9868,0.0102,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9960,0.0008,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9509,0.0779,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9943,0.0047,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.2942,0.9886,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9542,0.9900,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.1470,0.9966,0.0000</t>
+  </si>
+  <si>
+    <t>0.0030,0.2239,0.9794,0.0001</t>
+  </si>
+  <si>
+    <t>0.9851,0.0004,0.0055,0.0000</t>
+  </si>
+  <si>
+    <t>0.6881,0.0090,0.2375,0.0014</t>
+  </si>
+  <si>
+    <t>0.0765,0.0005,0.9643,0.0001</t>
+  </si>
+  <si>
+    <t>0.8848,0.0028,0.1185,0.0001</t>
+  </si>
+  <si>
+    <t>0.0204,0.0002,0.0005,0.9935</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9973,0.9443,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0013,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0100,0.9857,0.0024,0.0006</t>
-  </si>
-  <si>
-    <t>0.9927,0.0031,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0267,0.9701,0.0055,0.0001</t>
-  </si>
-  <si>
-    <t>0.9957,0.0004,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9254,0.0009,0.0034,0.0326</t>
-  </si>
-  <si>
-    <t>0.9984,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0741,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.9795,0.0001,0.0063,0.0006</t>
-  </si>
-  <si>
-    <t>0.0563,0.8988,0.0279,0.0009</t>
-  </si>
-  <si>
-    <t>0.9622,0.0227,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.9455,0.0255,0.0059,0.0002</t>
-  </si>
-  <si>
-    <t>0.0201,0.9733,0.0039,0.0005</t>
-  </si>
-  <si>
-    <t>0.4857,0.4206,0.0188,0.0010</t>
-  </si>
-  <si>
-    <t>0.9605,0.0394,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9879,0.0087,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9978,0.0006,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9902,0.0075,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9967,0.0016,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9963,0.0020,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9956,0.0029,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9959,0.0011,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0578,0.9375,0.0111,0.0004</t>
-  </si>
-  <si>
-    <t>0.1533,0.8443,0.0158,0.0002</t>
-  </si>
-  <si>
-    <t>0.1144,0.9184,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.6655,0.3677,0.0101,0.0007</t>
-  </si>
-  <si>
-    <t>0.4095,0.6760,0.0038,0.0003</t>
-  </si>
-  <si>
-    <t>0.8753,0.1259,0.0103,0.0009</t>
-  </si>
-  <si>
-    <t>0.9555,0.0160,0.0151,0.0003</t>
-  </si>
-  <si>
-    <t>0.5755,0.2744,0.1644,0.0040</t>
-  </si>
-  <si>
-    <t>0.0000,0.0749,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.1141,0.3209,0.7690,0.0013</t>
-  </si>
-  <si>
-    <t>0.0001,0.0027,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0037,0.0366,0.9870,0.0006</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0224,0.2057,0.8203,0.0005</t>
-  </si>
-  <si>
-    <t>0.0016,0.0479,0.9956,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0005,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0053,0.0043,0.9901,0.0003</t>
-  </si>
-  <si>
-    <t>0.0653,0.0054,0.9315,0.0004</t>
-  </si>
-  <si>
-    <t>0.0705,0.0068,0.9126,0.0006</t>
-  </si>
-  <si>
-    <t>0.0314,0.0314,0.9346,0.0004</t>
-  </si>
-  <si>
-    <t>0.0114,0.8818,0.1794,0.0002</t>
-  </si>
-  <si>
-    <t>0.3453,0.4823,0.0345,0.0003</t>
-  </si>
-  <si>
-    <t>0.7599,0.1139,0.0204,0.0022</t>
-  </si>
-  <si>
-    <t>0.5471,0.0068,0.5076,0.0008</t>
-  </si>
-  <si>
-    <t>0.0018,0.9971,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0371,0.9771,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0419,0.9580,0.0084,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.9987,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9524,0.0142,0.0055,0.0000</t>
-  </si>
-  <si>
-    <t>0.9840,0.0012,0.0032,0.0000</t>
-  </si>
-  <si>
-    <t>0.9382,0.0129,0.0084,0.0016</t>
-  </si>
-  <si>
-    <t>0.5612,0.0850,0.1829,0.0028</t>
-  </si>
-  <si>
-    <t>0.9022,0.0035,0.0652,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0008,0.9968,0.0051</t>
-  </si>
-  <si>
-    <t>0.0295,0.0120,0.9544,0.0004</t>
-  </si>
-  <si>
-    <t>0.0257,0.0495,0.9294,0.0004</t>
-  </si>
-  <si>
-    <t>0.0016,0.0509,0.9940,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.8636,0.9214,0.0001</t>
-  </si>
-  <si>
-    <t>0.9941,0.0030,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9826,0.0202,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.8789,0.1385,0.0010,0.0007</t>
-  </si>
-  <si>
-    <t>0.9676,0.0386,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9309,0.0631,0.0085,0.0006</t>
-  </si>
-  <si>
-    <t>0.9525,0.0412,0.0059,0.0021</t>
-  </si>
-  <si>
-    <t>0.9911,0.0068,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9919,0.0040,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0010,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0398,0.8298,0.1660,0.0005</t>
-  </si>
-  <si>
-    <t>0.9480,0.0058,0.0214,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0012,0.9987,0.0005</t>
-  </si>
-  <si>
-    <t>0.0052,0.0358,0.9836,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0014,0.9974,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0060,0.1252,0.9209,0.0025</t>
-  </si>
-  <si>
-    <t>0.0034,0.0123,0.9862,0.0010</t>
-  </si>
-  <si>
-    <t>0.8777,0.0064,0.0673,0.0012</t>
-  </si>
-  <si>
-    <t>0.7922,0.0004,0.2492,0.0001</t>
-  </si>
-  <si>
-    <t>0.9902,0.0021,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9372,0.0784,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.7270,0.3020,0.0159,0.0005</t>
-  </si>
-  <si>
-    <t>0.9903,0.0126,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9463,0.0564,0.0030,0.0005</t>
-  </si>
-  <si>
-    <t>0.9982,0.0011,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9211,0.1083,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.8781,0.1633,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9862,0.0104,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.0030,0.0120,0.9908,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.4382,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0023,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0165,0.9928,0.0004</t>
-  </si>
-  <si>
-    <t>0.0050,0.0007,0.9935,0.0001</t>
-  </si>
-  <si>
-    <t>0.1534,0.0005,0.8982,0.0003</t>
-  </si>
-  <si>
-    <t>0.4442,0.0055,0.5949,0.0004</t>
-  </si>
-  <si>
-    <t>0.0093,0.0083,0.9711,0.0044</t>
-  </si>
-  <si>
-    <t>0.9928,0.0007,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.0767,0.0330,0.0004,0.9425</t>
-  </si>
-  <si>
-    <t>0.0521,0.0004,0.0002,0.9876</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9956,0.0007,0.0006,0.0001</t>
+    <t>0.0003,0.0015,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9929,0.9844,0.0000</t>
+  </si>
+  <si>
+    <t>0.9917,0.0064,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0388,0.9661,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.9930,0.0017,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.0223,0.9743,0.0039,0.0001</t>
+  </si>
+  <si>
+    <t>0.9924,0.0008,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.9757,0.0005,0.0020,0.0047</t>
+  </si>
+  <si>
+    <t>0.9964,0.0011,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0352,0.9991,0.0003</t>
+  </si>
+  <si>
+    <t>0.9969,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9967,0.0006,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.0634,0.9127,0.0145,0.0005</t>
+  </si>
+  <si>
+    <t>0.9463,0.0316,0.0060,0.0003</t>
+  </si>
+  <si>
+    <t>0.9206,0.0478,0.0085,0.0003</t>
+  </si>
+  <si>
+    <t>0.0565,0.8863,0.0241,0.0014</t>
+  </si>
+  <si>
+    <t>0.8144,0.0772,0.0508,0.0006</t>
+  </si>
+  <si>
+    <t>0.7450,0.3161,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9848,0.0100,0.0015,0.0012</t>
+  </si>
+  <si>
+    <t>0.9960,0.0008,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9899,0.0087,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9956,0.0016,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9882,0.0082,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9959,0.0010,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9951,0.0031,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0989,0.9218,0.0039,0.0002</t>
+  </si>
+  <si>
+    <t>0.3082,0.6557,0.0303,0.0003</t>
+  </si>
+  <si>
+    <t>0.1388,0.8823,0.0062,0.0001</t>
+  </si>
+  <si>
+    <t>0.0396,0.4556,0.8471,0.0012</t>
+  </si>
+  <si>
+    <t>0.6121,0.4716,0.0048,0.0001</t>
+  </si>
+  <si>
+    <t>0.6904,0.3694,0.0044,0.0006</t>
+  </si>
+  <si>
+    <t>0.9549,0.0312,0.0098,0.0009</t>
+  </si>
+  <si>
+    <t>0.4797,0.4963,0.1095,0.0092</t>
+  </si>
+  <si>
+    <t>0.0000,0.0117,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.1287,0.1824,0.7899,0.0024</t>
+  </si>
+  <si>
+    <t>0.0000,0.0014,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0093,0.0401,0.9791,0.0004</t>
+  </si>
+  <si>
+    <t>0.0181,0.0002,0.9909,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.6761,0.9652,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0182,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0311,0.0026,0.9615,0.0003</t>
+  </si>
+  <si>
+    <t>0.0142,0.0034,0.9853,0.0001</t>
+  </si>
+  <si>
+    <t>0.7351,0.0237,0.1670,0.0009</t>
+  </si>
+  <si>
+    <t>0.1784,0.0509,0.6670,0.0006</t>
+  </si>
+  <si>
+    <t>0.0087,0.9219,0.1360,0.0001</t>
+  </si>
+  <si>
+    <t>0.8405,0.1194,0.0034,0.0001</t>
+  </si>
+  <si>
+    <t>0.8674,0.0117,0.0566,0.0024</t>
+  </si>
+  <si>
+    <t>0.6553,0.0041,0.4403,0.0002</t>
+  </si>
+  <si>
+    <t>0.0106,0.9861,0.0116,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.9980,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.0241,0.9797,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.0274,0.9699,0.0074,0.0003</t>
+  </si>
+  <si>
+    <t>0.0080,0.9904,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.4954,0.0141,0.5251,0.0005</t>
+  </si>
+  <si>
+    <t>0.8923,0.0005,0.1413,0.0000</t>
+  </si>
+  <si>
+    <t>0.9344,0.0079,0.0206,0.0007</t>
+  </si>
+  <si>
+    <t>0.4173,0.0068,0.6176,0.0005</t>
+  </si>
+  <si>
+    <t>0.7660,0.0008,0.2701,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.0004,0.9955,0.0080</t>
+  </si>
+  <si>
+    <t>0.0095,0.0305,0.9790,0.0004</t>
+  </si>
+  <si>
+    <t>0.0869,0.0030,0.9227,0.0003</t>
+  </si>
+  <si>
+    <t>0.0329,0.0598,0.9324,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.7970,0.9604,0.0001</t>
+  </si>
+  <si>
+    <t>0.9927,0.0053,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9770,0.0279,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9289,0.0858,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9739,0.0299,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.7009,0.2487,0.0500,0.0014</t>
+  </si>
+  <si>
+    <t>0.9466,0.0475,0.0060,0.0011</t>
+  </si>
+  <si>
+    <t>0.9899,0.0068,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9989,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0194,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0205,0.9147,0.1060,0.0006</t>
+  </si>
+  <si>
+    <t>0.7973,0.0032,0.1509,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9993,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.0029,0.9981,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.9324,0.8116,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0007,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0043,0.0012,0.9914,0.0005</t>
+  </si>
+  <si>
+    <t>0.0022,0.0101,0.9894,0.0011</t>
+  </si>
+  <si>
+    <t>0.2909,0.0065,0.6541,0.0043</t>
+  </si>
+  <si>
+    <t>0.8640,0.0002,0.1812,0.0001</t>
+  </si>
+  <si>
+    <t>0.9534,0.0021,0.0255,0.0002</t>
+  </si>
+  <si>
+    <t>0.9654,0.0385,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.7833,0.2280,0.0162,0.0006</t>
+  </si>
+  <si>
+    <t>0.9921,0.0062,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.5418,0.4514,0.0493,0.0014</t>
+  </si>
+  <si>
+    <t>0.9949,0.0052,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9788,0.0210,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9465,0.0642,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9783,0.0201,0.0016,0.0008</t>
+  </si>
+  <si>
+    <t>0.0051,0.0188,0.9807,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0038,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0058,0.9988,0.0003</t>
+  </si>
+  <si>
+    <t>0.0220,0.1962,0.8427,0.0004</t>
+  </si>
+  <si>
+    <t>0.0020,0.0004,0.9972,0.0001</t>
+  </si>
+  <si>
+    <t>0.0192,0.0123,0.9741,0.0005</t>
+  </si>
+  <si>
+    <t>0.0109,0.0026,0.9832,0.0003</t>
+  </si>
+  <si>
+    <t>0.0017,0.1374,0.9880,0.0004</t>
+  </si>
+  <si>
+    <t>0.9960,0.0005,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0081,0.1217,0.0001,0.9818</t>
+  </si>
+  <si>
+    <t>0.2031,0.0007,0.0002,0.9344</t>
+  </si>
+  <si>
+    <t>0.9938,0.0006,0.0008,0.0001</t>
   </si>
 </sst>
 </file>
@@ -1953,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,7 +1973,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,7 +2001,7 @@
         <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2009,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2023,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2037,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2051,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2065,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2079,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2093,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2107,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,7 +2141,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,7 +2155,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,7 +2169,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2191,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2205,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,7 +2225,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2247,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2258,10 +2264,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2272,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,7 +2295,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,7 +2309,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,7 +2323,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2328,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,7 +2365,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,7 +2379,7 @@
         <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,7 +2407,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2426,10 +2432,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,7 +2449,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2468,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,7 +2491,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,7 +2505,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,7 +2519,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,7 +2533,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2566,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,7 +2589,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,7 +2645,7 @@
         <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,7 +2659,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,7 +2701,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2709,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2723,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2737,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2765,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2776,10 +2782,10 @@
         <v>259</v>
       </c>
       <c r="C61" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2793,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,7 +2813,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,7 +2827,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,7 +2855,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2863,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,7 +2883,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2891,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,7 +2925,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2930,10 +2936,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,7 +2953,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2958,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,7 +2995,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,7 +3009,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,7 +3023,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,7 +3037,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,7 +3051,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,7 +3065,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,7 +3079,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,7 +3093,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,7 +3107,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,7 +3121,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3126,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,7 +3149,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3154,10 +3160,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3171,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3185,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3199,7 +3205,7 @@
         <v>262</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3213,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3227,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3241,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3252,10 +3258,10 @@
         <v>259</v>
       </c>
       <c r="C95" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3269,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3283,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3297,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3311,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3325,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3339,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3353,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3367,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3381,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3395,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,7 +3415,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,7 +3443,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3521,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,7 +3541,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,7 +3555,7 @@
         <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3560,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3574,10 +3580,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,7 +3597,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3602,10 +3608,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3619,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,7 +3653,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,7 +3667,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,7 +3681,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,7 +3695,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,7 +3709,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3717,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3731,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3745,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3759,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3773,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3787,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3801,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3815,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>370</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,7 +3835,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,7 +3849,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,7 +3863,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,7 +3877,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3896,10 +3902,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,7 +3919,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,7 +3947,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,7 +3961,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,7 +3975,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,7 +3989,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,7 +4003,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4011,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,7 +4031,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4039,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,7 +4059,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4067,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4095,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,7 +4115,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4137,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>272</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,7 +4157,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,7 +4199,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4235,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4249,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4263,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4277,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4291,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4305,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4319,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4333,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,7 +4353,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,7 +4367,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,7 +4381,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4386,10 +4392,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4400,10 +4406,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4417,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4431,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4442,10 +4448,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4473,7 +4479,7 @@
         <v>261</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4526,10 +4532,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,7 +4591,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,7 +4605,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4610,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,7 +4633,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,7 +4647,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,7 +4661,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4680,10 +4686,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,7 +4703,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,7 +4717,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,7 +4731,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,7 +4745,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,7 +4759,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4764,10 +4770,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4806,10 +4812,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,7 +4843,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,7 +4857,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,7 +4871,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,7 +4885,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,7 +4899,7 @@
         <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4907,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4921,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4935,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4949,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4963,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4977,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4991,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5005,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,7 +5039,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5086,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5103,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,7 +5123,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5131,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,7 +5151,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,7 +5165,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5170,10 +5176,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5215,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5229,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5243,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5257,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5271,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5285,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5299,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5313,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,7 +5361,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,7 +5375,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,7 +5389,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,7 +5403,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,7 +5417,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,7 +5431,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,7 +5445,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,7 +5459,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,7 +5473,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,7 +5487,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>410</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,7 +5501,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
